--- a/data/trans_orig/P33B_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R2-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>60168</t>
+          <t>63370</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46945</t>
+          <t>47971</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75522</t>
+          <t>80158</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>64802</t>
+          <t>72268</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53755</t>
+          <t>59659</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77512</t>
+          <t>86018</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>124970</t>
+          <t>135638</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108371</t>
+          <t>117491</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145645</t>
+          <t>159521</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>445044</t>
+          <t>487248</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>429690</t>
+          <t>470460</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>458267</t>
+          <t>502647</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>382665</t>
+          <t>416143</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>369955</t>
+          <t>402393</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>393712</t>
+          <t>428752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>827709</t>
+          <t>903391</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>807034</t>
+          <t>879508</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>844308</t>
+          <t>921538</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,69%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55604</t>
+          <t>57518</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42425</t>
+          <t>43491</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69678</t>
+          <t>73250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>69467</t>
+          <t>79412</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58147</t>
+          <t>67480</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82544</t>
+          <t>93207</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>125071</t>
+          <t>136930</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107772</t>
+          <t>119085</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>144151</t>
+          <t>157812</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>396609</t>
+          <t>425694</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>382535</t>
+          <t>409962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>409788</t>
+          <t>439721</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313113</t>
+          <t>343731</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>300036</t>
+          <t>329936</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>324433</t>
+          <t>355663</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>709722</t>
+          <t>769425</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>690642</t>
+          <t>748543</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>727021</t>
+          <t>787270</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,86%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>79201</t>
+          <t>85520</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31016</t>
+          <t>68011</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>132636</t>
+          <t>100711</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44334</t>
+          <t>50029</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35423</t>
+          <t>39839</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53709</t>
+          <t>59943</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>123535</t>
+          <t>135549</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58486</t>
+          <t>117905</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>180678</t>
+          <t>155003</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>589063</t>
+          <t>386092</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535628</t>
+          <t>370901</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637248</t>
+          <t>403601</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>122577</t>
+          <t>137468</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113202</t>
+          <t>127554</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131488</t>
+          <t>147658</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>711640</t>
+          <t>523560</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>654497</t>
+          <t>504106</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>776689</t>
+          <t>541204</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>82,11%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>165386</t>
+          <t>183161</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>142711</t>
+          <t>159254</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189539</t>
+          <t>208436</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>161748</t>
+          <t>180985</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92835</t>
+          <t>161247</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>212504</t>
+          <t>201138</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>327134</t>
+          <t>364147</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>225931</t>
+          <t>334584</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>374587</t>
+          <t>393455</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>869433</t>
+          <t>948682</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>845280</t>
+          <t>923407</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>892108</t>
+          <t>972589</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>816346</t>
+          <t>680226</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>765590</t>
+          <t>660073</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>885259</t>
+          <t>699964</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1685778</t>
+          <t>1628907</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1638325</t>
+          <t>1599599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1786981</t>
+          <t>1658470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>77816</t>
+          <t>84860</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63191</t>
+          <t>67607</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97091</t>
+          <t>104899</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>218863</t>
+          <t>244957</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>166396</t>
+          <t>224126</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>253584</t>
+          <t>268000</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>296680</t>
+          <t>329817</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>237969</t>
+          <t>303207</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>328663</t>
+          <t>359555</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>396200</t>
+          <t>482022</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>376925</t>
+          <t>461983</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>410825</t>
+          <t>499275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>620133</t>
+          <t>585170</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>585412</t>
+          <t>562127</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>672600</t>
+          <t>606001</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1016332</t>
+          <t>1067192</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>984349</t>
+          <t>1037454</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1075043</t>
+          <t>1093802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>78,3%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10706</t>
+          <t>11307</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26168</t>
+          <t>24072</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>177719</t>
+          <t>197781</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>159028</t>
+          <t>176544</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>199193</t>
+          <t>218604</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>188425</t>
+          <t>209087</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>165860</t>
+          <t>187204</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>214102</t>
+          <t>235503</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>229801</t>
+          <t>225921</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>214339</t>
+          <t>213156</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236940</t>
+          <t>232812</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>583652</t>
+          <t>646500</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>562178</t>
+          <t>625677</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>602343</t>
+          <t>667737</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>813453</t>
+          <t>872422</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>787776</t>
+          <t>846006</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>836018</t>
+          <t>894305</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>448881</t>
+          <t>485736</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>351024</t>
+          <t>447278</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>499304</t>
+          <t>527152</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>736933</t>
+          <t>825431</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>600872</t>
+          <t>782979</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>801638</t>
+          <t>866477</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1185814</t>
+          <t>1311168</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1024802</t>
+          <t>1251953</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1276728</t>
+          <t>1374055</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2926150</t>
+          <t>2955658</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2875727</t>
+          <t>2914242</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3024007</t>
+          <t>2994116</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2838485</t>
+          <t>2809239</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2773780</t>
+          <t>2768193</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2974546</t>
+          <t>2851691</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5764635</t>
+          <t>5764896</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5673721</t>
+          <t>5702009</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5925647</t>
+          <t>5824111</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>82,31%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3375031</t>
+          <t>3441394</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3375031</t>
+          <t>3441394</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3375031</t>
+          <t>3441394</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6950449</t>
+          <t>7076064</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6950449</t>
+          <t>7076064</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6950449</t>
+          <t>7076064</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
